--- a/JsonConverter/ExcelFiles/Monster.xlsx
+++ b/JsonConverter/ExcelFiles/Monster.xlsx
@@ -19,99 +19,102 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
+  <x:si>
+    <x:t>BaseAttack</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DetectRange</x:t>
+  </x:si>
   <x:si>
     <x:t>PatrolRange</x:t>
   </x:si>
   <x:si>
+    <x:t>스폰 지점 이탈 제한</x:t>
+  </x:si>
+  <x:si>
+    <x:t>테스트용 몹이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoveSpeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고블린</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_goblin_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SpawnLimitRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 표기용 Icon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+  </x:si>
+  <x:si>
     <x:t>이동속도</x:t>
   </x:si>
   <x:si>
-    <x:t>DetectRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스폰 지점 이탈 제한</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseAttack</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고블린</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SpawnLimitRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>테스트용 몹이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_goblin_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+    <x:t>감지 거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배회 반경</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
     <x:t>BaseHp</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
+    <x:t>몬스터의 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명</x:t>
   </x:si>
   <x:si>
     <x:t>기본 공격력</x:t>
   </x:si>
   <x:si>
+    <x:t>기본 체력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 표기용 Icon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터의 이름</x:t>
-  </x:si>
-  <x:si>
     <x:t>공격 사거리</x:t>
   </x:si>
   <x:si>
-    <x:t>감지 거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 체력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배회 반경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MoveSpeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명</x:t>
+    <x:t>DropEXP</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -159,26 +162,11 @@
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="&quot;맑은 고딕&quot;"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff008000"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="&quot;맑은 고딕&quot;"/>
-          <x:sz val="11"/>
-          <x:color rgb="ff008000"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <x:font>
+      <x:name val="&quot;맑은 고딕&quot;"/>
+      <x:sz val="11"/>
+      <x:color rgb="ff008000"/>
+    </x:font>
   </x:fonts>
   <x:fills count="8">
     <x:fill>
@@ -923,454 +911,498 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:L35"/>
+  <x:dimension ref="A1:O35"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
     <x:col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
-    <x:col min="3" max="3" width="60.5703125" style="3" customWidth="1"/>
-    <x:col min="4" max="4" width="30.5703125" style="3" customWidth="1"/>
-    <x:col min="5" max="5" width="20.28515625" style="3" customWidth="1"/>
-    <x:col min="6" max="6" width="11.4296875" style="3" customWidth="1"/>
-    <x:col min="7" max="7" width="16.5703125" style="3" customWidth="1"/>
-    <x:col min="8" max="8" width="14.14453125" style="3" customWidth="1"/>
-    <x:col min="9" max="9" width="14.71484375" style="3" customWidth="1"/>
-    <x:col min="10" max="10" width="17.85546875" style="14" customWidth="1"/>
-    <x:col min="11" max="11" width="18.5703125" style="3" customWidth="1"/>
-    <x:col min="12" max="12" width="13.4296875" style="3" customWidth="1"/>
-    <x:col min="13" max="16384" width="12.5703125" style="3"/>
+    <x:col min="3" max="3" width="19.5703125" customWidth="1"/>
+    <x:col min="4" max="4" width="60.5703125" style="3" customWidth="1"/>
+    <x:col min="5" max="5" width="30.5703125" style="3" customWidth="1"/>
+    <x:col min="6" max="6" width="20.28515625" style="3" customWidth="1"/>
+    <x:col min="7" max="7" width="11.4296875" style="3" customWidth="1"/>
+    <x:col min="8" max="8" width="16.5703125" style="3" customWidth="1"/>
+    <x:col min="9" max="9" width="14.14453125" style="3" customWidth="1"/>
+    <x:col min="10" max="10" width="14.71484375" style="3" customWidth="1"/>
+    <x:col min="11" max="11" width="17.85546875" style="14" customWidth="1"/>
+    <x:col min="12" max="12" width="18.5703125" style="3" customWidth="1"/>
+    <x:col min="13" max="13" width="13.4296875" style="3" customWidth="1"/>
+    <x:col min="14" max="14" width="12.5703125" style="3"/>
+    <x:col min="15" max="15" width="19.5703125" style="3" customWidth="1"/>
+    <x:col min="16" max="16384" width="12.5703125" style="3"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:12" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s">
+      <x:c r="D1" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J1" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K1" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H1" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I1" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="J1" s="14" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K1" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="L1" s="3" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:12" ht="13.199999999999999">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M1" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="O1" s="1"/>
+    </x:row>
+    <x:row r="2" spans="1:15" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="J2" s="14" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="K2" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K2" s="14" t="s">
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L2" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:12" s="11" customFormat="1" ht="15.75" customHeight="1">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="M2" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="N2" s="3" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="O2" s="1"/>
+    </x:row>
+    <x:row r="3" spans="1:15" s="11" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D3" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H3" s="12" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J3" s="12" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K3" s="13" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L3" s="11" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D3" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E3" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F3" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G3" s="12" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H3" s="12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I3" s="12" t="s">
+      <x:c r="M3" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J3" s="13" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K3" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="L3" s="11" t="s">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:10" ht="15.75" customHeight="1">
+      <x:c r="N3" s="11" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="O3" s="12"/>
+    </x:row>
+    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D4" s="10"/>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="E4" s="10"/>
-      <x:c r="F4" s="4">
+      <x:c r="F4" s="10"/>
+      <x:c r="G4" s="4">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G4" s="4">
+      <x:c r="H4" s="4">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="H4" s="4">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="I4" s="4">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J4" s="14">
+      <x:c r="J4" s="4">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K4" s="14">
         <x:v>1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="O4" s="4"/>
+    </x:row>
+    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4"/>
       <x:c r="B5" s="5"/>
-      <x:c r="C5" s="5"/>
-      <x:c r="D5" s="10"/>
+      <x:c r="D5" s="5"/>
       <x:c r="E5" s="10"/>
-      <x:c r="F5" s="5"/>
+      <x:c r="F5" s="10"/>
       <x:c r="G5" s="5"/>
       <x:c r="H5" s="5"/>
       <x:c r="I5" s="5"/>
-    </x:row>
-    <x:row r="6" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J5" s="5"/>
+      <x:c r="O5" s="5"/>
+    </x:row>
+    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="5"/>
       <x:c r="B6" s="5"/>
-      <x:c r="C6" s="5"/>
-      <x:c r="D6" s="10"/>
+      <x:c r="D6" s="5"/>
       <x:c r="E6" s="10"/>
-      <x:c r="F6" s="5"/>
+      <x:c r="F6" s="10"/>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="5"/>
       <x:c r="I6" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J6" s="5"/>
+      <x:c r="O6" s="5"/>
+    </x:row>
+    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="4"/>
       <x:c r="B7" s="4"/>
-      <x:c r="C7" s="4"/>
-      <x:c r="D7" s="10"/>
+      <x:c r="D7" s="4"/>
       <x:c r="E7" s="10"/>
-      <x:c r="F7" s="4"/>
+      <x:c r="F7" s="10"/>
       <x:c r="G7" s="4"/>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="4"/>
-    </x:row>
-    <x:row r="8" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J7" s="4"/>
+      <x:c r="O7" s="4"/>
+    </x:row>
+    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="4"/>
       <x:c r="B8" s="4"/>
-      <x:c r="C8" s="4"/>
-      <x:c r="D8" s="10"/>
+      <x:c r="D8" s="4"/>
       <x:c r="E8" s="10"/>
-      <x:c r="F8" s="4"/>
+      <x:c r="F8" s="10"/>
       <x:c r="G8" s="4"/>
       <x:c r="H8" s="4"/>
       <x:c r="I8" s="4"/>
-    </x:row>
-    <x:row r="9" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J8" s="4"/>
+      <x:c r="O8" s="4"/>
+    </x:row>
+    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="4"/>
       <x:c r="B9" s="4"/>
-      <x:c r="C9" s="4"/>
-      <x:c r="D9" s="10"/>
+      <x:c r="D9" s="4"/>
       <x:c r="E9" s="10"/>
-      <x:c r="F9" s="4"/>
+      <x:c r="F9" s="10"/>
       <x:c r="G9" s="4"/>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="4"/>
-    </x:row>
-    <x:row r="10" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J9" s="4"/>
+      <x:c r="O9" s="4"/>
+    </x:row>
+    <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1"/>
-      <x:c r="C10" s="1"/>
-      <x:c r="F10" s="1"/>
+      <x:c r="D10" s="1"/>
       <x:c r="G10" s="1"/>
       <x:c r="H10" s="1"/>
       <x:c r="I10" s="1"/>
-    </x:row>
-    <x:row r="11" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J10" s="1"/>
+      <x:c r="O10" s="1"/>
+    </x:row>
+    <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1"/>
-      <x:c r="C11" s="1"/>
-      <x:c r="F11" s="1"/>
+      <x:c r="D11" s="1"/>
       <x:c r="G11" s="1"/>
       <x:c r="H11" s="1"/>
       <x:c r="I11" s="1"/>
-    </x:row>
-    <x:row r="12" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J11" s="1"/>
+      <x:c r="O11" s="1"/>
+    </x:row>
+    <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A12" s="6"/>
       <x:c r="B12" s="6"/>
-      <x:c r="C12" s="6"/>
-      <x:c r="F12" s="6"/>
+      <x:c r="D12" s="6"/>
       <x:c r="G12" s="6"/>
       <x:c r="H12" s="6"/>
       <x:c r="I12" s="6"/>
-    </x:row>
-    <x:row r="13" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J12" s="6"/>
+      <x:c r="O12" s="6"/>
+    </x:row>
+    <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A13" s="6"/>
       <x:c r="B13" s="6"/>
-      <x:c r="C13" s="6"/>
-      <x:c r="F13" s="6"/>
+      <x:c r="D13" s="6"/>
       <x:c r="G13" s="6"/>
       <x:c r="H13" s="6"/>
       <x:c r="I13" s="6"/>
-    </x:row>
-    <x:row r="14" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J13" s="6"/>
+      <x:c r="O13" s="6"/>
+    </x:row>
+    <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1"/>
-      <x:c r="C14" s="1"/>
-      <x:c r="F14" s="1"/>
+      <x:c r="D14" s="1"/>
       <x:c r="G14" s="1"/>
       <x:c r="H14" s="1"/>
       <x:c r="I14" s="1"/>
-    </x:row>
-    <x:row r="15" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J14" s="1"/>
+      <x:c r="O14" s="1"/>
+    </x:row>
+    <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1"/>
-      <x:c r="C15" s="1"/>
-      <x:c r="F15" s="1"/>
+      <x:c r="D15" s="1"/>
       <x:c r="G15" s="1"/>
       <x:c r="H15" s="1"/>
       <x:c r="I15" s="1"/>
-    </x:row>
-    <x:row r="16" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J15" s="1"/>
+      <x:c r="O15" s="1"/>
+    </x:row>
+    <x:row r="16" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A16" s="7"/>
       <x:c r="B16" s="7"/>
-      <x:c r="C16" s="7"/>
-      <x:c r="F16" s="7"/>
+      <x:c r="D16" s="7"/>
       <x:c r="G16" s="7"/>
       <x:c r="H16" s="7"/>
       <x:c r="I16" s="7"/>
-    </x:row>
-    <x:row r="17" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J16" s="7"/>
+      <x:c r="O16" s="7"/>
+    </x:row>
+    <x:row r="17" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A17" s="7"/>
       <x:c r="B17" s="7"/>
-      <x:c r="C17" s="7"/>
-      <x:c r="F17" s="7"/>
+      <x:c r="D17" s="7"/>
       <x:c r="G17" s="7"/>
       <x:c r="H17" s="7"/>
       <x:c r="I17" s="7"/>
-    </x:row>
-    <x:row r="18" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J17" s="7"/>
+      <x:c r="O17" s="7"/>
+    </x:row>
+    <x:row r="18" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A18" s="7"/>
       <x:c r="B18" s="7"/>
-      <x:c r="C18" s="7"/>
-      <x:c r="F18" s="7"/>
+      <x:c r="D18" s="7"/>
       <x:c r="G18" s="7"/>
       <x:c r="H18" s="7"/>
       <x:c r="I18" s="7"/>
-    </x:row>
-    <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J18" s="7"/>
+      <x:c r="O18" s="7"/>
+    </x:row>
+    <x:row r="19" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A19" s="7"/>
       <x:c r="B19" s="7"/>
-      <x:c r="C19" s="7"/>
-      <x:c r="F19" s="7"/>
+      <x:c r="D19" s="7"/>
       <x:c r="G19" s="7"/>
       <x:c r="H19" s="7"/>
       <x:c r="I19" s="7"/>
-    </x:row>
-    <x:row r="20" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J19" s="7"/>
+      <x:c r="O19" s="7"/>
+    </x:row>
+    <x:row r="20" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A20" s="7"/>
       <x:c r="B20" s="7"/>
-      <x:c r="C20" s="7"/>
-      <x:c r="F20" s="7"/>
+      <x:c r="D20" s="7"/>
       <x:c r="G20" s="7"/>
       <x:c r="H20" s="7"/>
       <x:c r="I20" s="7"/>
-    </x:row>
-    <x:row r="21" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J20" s="7"/>
+      <x:c r="O20" s="7"/>
+    </x:row>
+    <x:row r="21" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A21" s="7"/>
       <x:c r="B21" s="7"/>
-      <x:c r="C21" s="7"/>
-      <x:c r="F21" s="7"/>
+      <x:c r="D21" s="7"/>
       <x:c r="G21" s="7"/>
       <x:c r="H21" s="7"/>
       <x:c r="I21" s="7"/>
-    </x:row>
-    <x:row r="22" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J21" s="7"/>
+      <x:c r="O21" s="7"/>
+    </x:row>
+    <x:row r="22" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A22" s="7"/>
       <x:c r="B22" s="7"/>
-      <x:c r="C22" s="7"/>
-      <x:c r="F22" s="7"/>
+      <x:c r="D22" s="7"/>
       <x:c r="G22" s="7"/>
       <x:c r="H22" s="7"/>
       <x:c r="I22" s="7"/>
-    </x:row>
-    <x:row r="23" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J22" s="7"/>
+      <x:c r="O22" s="7"/>
+    </x:row>
+    <x:row r="23" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A23" s="7"/>
       <x:c r="B23" s="7"/>
-      <x:c r="C23" s="7"/>
-      <x:c r="F23" s="7"/>
+      <x:c r="D23" s="7"/>
       <x:c r="G23" s="7"/>
       <x:c r="H23" s="7"/>
       <x:c r="I23" s="7"/>
-    </x:row>
-    <x:row r="24" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J23" s="7"/>
+      <x:c r="O23" s="7"/>
+    </x:row>
+    <x:row r="24" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A24" s="7"/>
       <x:c r="B24" s="7"/>
-      <x:c r="C24" s="7"/>
-      <x:c r="F24" s="7"/>
+      <x:c r="D24" s="7"/>
       <x:c r="G24" s="7"/>
       <x:c r="H24" s="7"/>
       <x:c r="I24" s="7"/>
-    </x:row>
-    <x:row r="25" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J24" s="7"/>
+      <x:c r="O24" s="7"/>
+    </x:row>
+    <x:row r="25" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A25" s="7"/>
       <x:c r="B25" s="7"/>
-      <x:c r="C25" s="7"/>
-      <x:c r="F25" s="7"/>
+      <x:c r="D25" s="7"/>
       <x:c r="G25" s="7"/>
       <x:c r="H25" s="7"/>
       <x:c r="I25" s="7"/>
-    </x:row>
-    <x:row r="26" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J25" s="7"/>
+      <x:c r="O25" s="7"/>
+    </x:row>
+    <x:row r="26" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A26" s="8"/>
       <x:c r="B26" s="8"/>
-      <x:c r="C26" s="8"/>
-      <x:c r="F26" s="8"/>
+      <x:c r="D26" s="8"/>
       <x:c r="G26" s="8"/>
       <x:c r="H26" s="8"/>
       <x:c r="I26" s="8"/>
-    </x:row>
-    <x:row r="27" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J26" s="8"/>
+      <x:c r="O26" s="8"/>
+    </x:row>
+    <x:row r="27" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A27" s="8"/>
       <x:c r="B27" s="8"/>
-      <x:c r="C27" s="8"/>
-      <x:c r="F27" s="8"/>
+      <x:c r="D27" s="8"/>
       <x:c r="G27" s="8"/>
       <x:c r="H27" s="8"/>
       <x:c r="I27" s="8"/>
-    </x:row>
-    <x:row r="28" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J27" s="8"/>
+      <x:c r="O27" s="8"/>
+    </x:row>
+    <x:row r="28" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A28" s="8"/>
       <x:c r="B28" s="8"/>
-      <x:c r="C28" s="8"/>
-      <x:c r="F28" s="8"/>
+      <x:c r="D28" s="8"/>
       <x:c r="G28" s="8"/>
       <x:c r="H28" s="8"/>
       <x:c r="I28" s="8"/>
-    </x:row>
-    <x:row r="29" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J28" s="8"/>
+      <x:c r="O28" s="8"/>
+    </x:row>
+    <x:row r="29" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A29" s="8"/>
       <x:c r="B29" s="8"/>
-      <x:c r="C29" s="8"/>
-      <x:c r="F29" s="8"/>
+      <x:c r="D29" s="8"/>
       <x:c r="G29" s="8"/>
       <x:c r="H29" s="8"/>
       <x:c r="I29" s="8"/>
-    </x:row>
-    <x:row r="30" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J29" s="8"/>
+      <x:c r="O29" s="8"/>
+    </x:row>
+    <x:row r="30" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A30" s="8"/>
       <x:c r="B30" s="8"/>
-      <x:c r="C30" s="8"/>
-      <x:c r="F30" s="8"/>
+      <x:c r="D30" s="8"/>
       <x:c r="G30" s="8"/>
       <x:c r="H30" s="8"/>
       <x:c r="I30" s="8"/>
-    </x:row>
-    <x:row r="31" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J30" s="8"/>
+      <x:c r="O30" s="8"/>
+    </x:row>
+    <x:row r="31" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A31" s="8"/>
       <x:c r="B31" s="8"/>
-      <x:c r="C31" s="8"/>
-      <x:c r="F31" s="8"/>
+      <x:c r="D31" s="8"/>
       <x:c r="G31" s="8"/>
       <x:c r="H31" s="8"/>
       <x:c r="I31" s="8"/>
-    </x:row>
-    <x:row r="32" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J31" s="8"/>
+      <x:c r="O31" s="8"/>
+    </x:row>
+    <x:row r="32" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A32" s="9"/>
       <x:c r="B32" s="9"/>
-      <x:c r="C32" s="9"/>
-      <x:c r="F32" s="9"/>
+      <x:c r="D32" s="9"/>
       <x:c r="G32" s="9"/>
       <x:c r="H32" s="9"/>
       <x:c r="I32" s="9"/>
-    </x:row>
-    <x:row r="33" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J32" s="9"/>
+      <x:c r="O32" s="9"/>
+    </x:row>
+    <x:row r="33" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A33" s="9"/>
       <x:c r="B33" s="9"/>
-      <x:c r="C33" s="9"/>
-      <x:c r="F33" s="9"/>
+      <x:c r="D33" s="9"/>
       <x:c r="G33" s="9"/>
       <x:c r="H33" s="9"/>
       <x:c r="I33" s="9"/>
-    </x:row>
-    <x:row r="34" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J33" s="9"/>
+      <x:c r="O33" s="9"/>
+    </x:row>
+    <x:row r="34" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A34" s="9"/>
       <x:c r="B34" s="9"/>
-      <x:c r="C34" s="9"/>
-      <x:c r="F34" s="9"/>
+      <x:c r="D34" s="9"/>
       <x:c r="G34" s="9"/>
       <x:c r="H34" s="9"/>
       <x:c r="I34" s="9"/>
-    </x:row>
-    <x:row r="35" spans="1:9" ht="15.75" customHeight="1">
+      <x:c r="J34" s="9"/>
+      <x:c r="O34" s="9"/>
+    </x:row>
+    <x:row r="35" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A35" s="9"/>
       <x:c r="B35" s="9"/>
-      <x:c r="C35" s="9"/>
-      <x:c r="F35" s="9"/>
+      <x:c r="D35" s="9"/>
       <x:c r="G35" s="9"/>
       <x:c r="H35" s="9"/>
       <x:c r="I35" s="9"/>
+      <x:c r="J35" s="9"/>
+      <x:c r="O35" s="9"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>
